--- a/backend/app/resources/templates/模板-焊材气体.xlsx
+++ b/backend/app/resources/templates/模板-焊材气体.xlsx
@@ -1,297 +1,199 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\工作\AI\PRD编写夹 - Workbuddy专用\demo\模板\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="焊材" sheetId="2" r:id="rId1"/>
-    <sheet name="气" sheetId="3" r:id="rId2"/>
+    <sheet name="焊材" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="气" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="DATA_START" localSheetId="0">焊材!$A$2</definedName>
     <definedName name="DATA_START" localSheetId="1">气!$A$2</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="23">
-  <si>
-    <t>焊材</t>
-  </si>
-  <si>
-    <t>结余</t>
-  </si>
-  <si>
-    <t>1月</t>
-  </si>
-  <si>
-    <t>2月</t>
-  </si>
-  <si>
-    <t>3月</t>
-  </si>
-  <si>
-    <t>4月</t>
-  </si>
-  <si>
-    <t>5月</t>
-  </si>
-  <si>
-    <t>6月</t>
-  </si>
-  <si>
-    <t>7月</t>
-  </si>
-  <si>
-    <t>8月</t>
-  </si>
-  <si>
-    <t>9月</t>
-  </si>
-  <si>
-    <t>10月</t>
-  </si>
-  <si>
-    <t>11月</t>
-  </si>
-  <si>
-    <t>12月</t>
-  </si>
-  <si>
-    <t>合计</t>
-  </si>
-  <si>
-    <t>DATA_START</t>
-  </si>
-  <si>
-    <t>乌兰察布储能项目</t>
-  </si>
-  <si>
-    <t>大唐雷州发电项目</t>
-  </si>
-  <si>
-    <t>新疆慧能项目</t>
-  </si>
-  <si>
-    <t>龙源纸业项目</t>
-  </si>
-  <si>
-    <t>内蒙古宜化项目</t>
-  </si>
-  <si>
-    <t>福建南平项目</t>
-  </si>
-  <si>
-    <t>气</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="23">
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+    </font>
+    <font>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <b val="1"/>
       <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -606,173 +508,174 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1037,7 +940,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
-    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{9DBC6A80-2C55-45C2-BCCC-05CE905CFABE}">
+    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1046,7 +949,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{826D0EAF-9BE4-47D8-A1D3-2CA9AF36B8AE}">
+    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1059,16 +962,7 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <colors>
-    <mruColors>
-      <color rgb="00FF0000"/>
-    </mruColors>
-  </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors/>
 </styleSheet>
 </file>
 
@@ -1320,667 +1214,759 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr codeName="Sheet2">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="18.3416666666667" customWidth="1"/>
-    <col min="2" max="2" width="13.3416666666667" customWidth="1"/>
-    <col min="3" max="14" width="7.84166666666667" customWidth="1"/>
-    <col min="15" max="15" width="8.84166666666667" customWidth="1"/>
+    <col width="18.3416666666667" customWidth="1" style="6" min="1" max="1"/>
+    <col width="22" customWidth="1" style="6" min="2" max="2"/>
+    <col width="7.84166666666667" customWidth="1" style="6" min="3" max="14"/>
+    <col width="8.84166666666667" customWidth="1" style="6" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1" spans="1:15">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
+    <row r="1" ht="22.5" customHeight="1" s="6">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>焊材</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2025-11及之前</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>1月</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2月</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>3月</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>7月</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>10月</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>11月</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>12月</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
       </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1" spans="1:15">
-      <c r="A2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="3">
+    <row r="2" ht="22.5" customHeight="1" s="6">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>DATA_START</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n">
         <v>221889.32</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="4" t="n">
         <v>3596</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4">
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n">
         <v>884.96</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="4" t="n">
         <v>13463.28</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="4" t="n">
         <v>1140</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="4" t="n">
         <v>5990</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="4" t="n">
         <v>1040.27</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="4" t="n">
         <v>665</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
+      <c r="K2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="4" t="n"/>
       <c r="O2" s="4">
-        <f t="shared" ref="O2:O8" si="0">SUM(B2:N2)</f>
-        <v>248668.83</v>
+        <f>SUM(B2:N2)</f>
+        <v/>
       </c>
     </row>
-    <row r="3" ht="22.5" customHeight="1" spans="1:15">
-      <c r="A3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="3">
+    <row r="3" ht="22.5" customHeight="1" s="6">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>乌兰察布储能项目</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
         <v>136337.32</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="4" t="n">
         <v>3596</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4">
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n">
         <v>1404</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
       <c r="O3" s="4">
-        <f t="shared" si="0"/>
-        <v>141337.32</v>
+        <f>SUM(B3:N3)</f>
+        <v/>
       </c>
     </row>
-    <row r="4" ht="22.5" customHeight="1" spans="1:15">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="3">
+    <row r="4" ht="22.5" customHeight="1" s="6">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>大唐雷州发电项目</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
         <v>77652.19</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
       <c r="O4" s="4">
-        <f t="shared" si="0"/>
-        <v>77652.19</v>
+        <f>SUM(B4:N4)</f>
+        <v/>
       </c>
     </row>
-    <row r="5" ht="22.5" customHeight="1" spans="1:15">
-      <c r="A5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="3">
+    <row r="5" ht="22.5" customHeight="1" s="6">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>新疆慧能项目</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
         <v>1838141.56</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="4" t="n">
         <v>29185.84</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="4" t="n"/>
       <c r="E5" s="4">
         <f>12106.2+973.45</f>
-        <v>13079.65</v>
-      </c>
-      <c r="F5" s="4">
+        <v/>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>360132.75</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="4" t="n">
         <v>23185.85</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="4" t="n">
         <v>32980</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="4" t="n">
         <v>26951.33</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="4" t="n">
         <v>67831.87</v>
       </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
       <c r="O5" s="4">
-        <f t="shared" si="0"/>
-        <v>2391488.85</v>
+        <f>SUM(B5:N5)</f>
+        <v/>
       </c>
     </row>
-    <row r="6" ht="22.5" customHeight="1" spans="1:15">
-      <c r="A6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4">
-        <v>514.56</v>
-      </c>
-      <c r="E6" s="4">
+    <row r="6" ht="22.5" customHeight="1" s="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>龙源纸业项目</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n">
+        <v>514.5599999999999</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>372.82</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="4" t="n">
         <v>372.82</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="4" t="n">
         <v>838.83</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="4" t="n">
         <v>672</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="4" t="n">
         <v>1118.45</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="4" t="n">
         <v>3821.36</v>
       </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
       <c r="O6" s="4">
-        <f t="shared" si="0"/>
-        <v>7710.84</v>
+        <f>SUM(B6:N6)</f>
+        <v/>
       </c>
     </row>
-    <row r="7" ht="22.5" customHeight="1" spans="1:15">
-      <c r="A7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
+    <row r="7" ht="22.5" customHeight="1" s="6">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>内蒙古宜化项目</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
       <c r="E7" s="4">
         <f>6380+30973.45</f>
-        <v>37353.45</v>
-      </c>
-      <c r="F7" s="4">
+        <v/>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="4" t="n">
         <v>27544.38</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="4" t="n">
         <v>7975</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="4" t="n">
         <v>17009.92</v>
       </c>
-      <c r="J7" s="4">
-        <v>8608.37</v>
-      </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
+      <c r="J7" s="4" t="n">
+        <v>8608.370000000001</v>
+      </c>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
       <c r="O7" s="4">
-        <f t="shared" si="0"/>
-        <v>98581.12</v>
+        <f>SUM(B7:N7)</f>
+        <v/>
       </c>
     </row>
-    <row r="8" ht="22.5" customHeight="1" spans="1:15">
-      <c r="A8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4">
+    <row r="8" ht="22.5" customHeight="1" s="6">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>福建南平项目</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n">
         <v>13323.01</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="4" t="n">
         <v>32101.36</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="4" t="n">
         <v>25817.5</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="4" t="n">
         <v>10670.35</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="4" t="n">
         <v>2379.65</v>
       </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
       <c r="O8" s="4">
-        <f t="shared" si="0"/>
-        <v>84291.87</v>
+        <f>SUM(B8:N8)</f>
+        <v/>
       </c>
     </row>
-    <row r="9" ht="22.5" customHeight="1" spans="1:15">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
+    <row r="9" ht="22.5" customHeight="1" s="6">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
       <c r="C9" s="5">
-        <f t="shared" ref="C9:N9" si="1">SUM(C2:C8)</f>
-        <v>36377.84</v>
+        <f>SUM(C2:C8)</f>
+        <v/>
       </c>
       <c r="D9" s="5">
-        <f t="shared" si="1"/>
-        <v>514.56</v>
+        <f>SUM(D2:D8)</f>
+        <v/>
       </c>
       <c r="E9" s="5">
-        <f t="shared" si="1"/>
-        <v>51690.88</v>
+        <f>SUM(E2:E8)</f>
+        <v/>
       </c>
       <c r="F9" s="5">
-        <f t="shared" si="1"/>
-        <v>387381.86</v>
+        <f>SUM(F2:F8)</f>
+        <v/>
       </c>
       <c r="G9" s="5">
-        <f t="shared" si="1"/>
-        <v>84810.42</v>
+        <f>SUM(G2:G8)</f>
+        <v/>
       </c>
       <c r="H9" s="5">
-        <f t="shared" si="1"/>
-        <v>74838.5</v>
+        <f>SUM(H2:H8)</f>
+        <v/>
       </c>
       <c r="I9" s="5">
-        <f t="shared" si="1"/>
-        <v>56790.32</v>
+        <f>SUM(I2:I8)</f>
+        <v/>
       </c>
       <c r="J9" s="5">
-        <f t="shared" si="1"/>
-        <v>83306.25</v>
+        <f>SUM(J2:J8)</f>
+        <v/>
       </c>
       <c r="K9" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(K2:K8)</f>
+        <v/>
       </c>
       <c r="L9" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(L2:L8)</f>
+        <v/>
       </c>
       <c r="M9" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(M2:M8)</f>
+        <v/>
       </c>
       <c r="N9" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(N2:N8)</f>
+        <v/>
       </c>
       <c r="O9" s="5">
         <f>SUBTOTAL(9,O2:O8)</f>
-        <v>3049731.02</v>
+        <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="18.3416666666667" customWidth="1"/>
-    <col min="2" max="2" width="13.3416666666667" customWidth="1"/>
-    <col min="3" max="14" width="7.84166666666667" customWidth="1"/>
-    <col min="15" max="15" width="8.84166666666667" customWidth="1"/>
+    <col width="18.3416666666667" customWidth="1" style="6" min="1" max="1"/>
+    <col width="22" customWidth="1" style="6" min="2" max="2"/>
+    <col width="7.84166666666667" customWidth="1" style="6" min="3" max="14"/>
+    <col width="8.84166666666667" customWidth="1" style="6" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1" spans="1:15">
-      <c r="A1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
+    <row r="1" ht="22.5" customHeight="1" s="6">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>气</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2025-11及之前</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>1月</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2月</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>3月</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>7月</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>10月</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>11月</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>12月</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
       </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1" spans="1:15">
-      <c r="A2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="3">
+    <row r="2" ht="22.5" customHeight="1" s="6">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>DATA_START</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n">
         <v>178692.35</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="4" t="n">
         <v>11123.01</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4">
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n">
         <v>17009.74</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="4" t="n">
         <v>10650.45</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="4" t="n">
         <v>4769.03</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="4" t="n">
         <v>3679</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="4" t="n">
         <v>3951.33</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="4" t="n">
         <v>3832.75</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
+      <c r="K2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="4" t="n"/>
       <c r="O2" s="4">
-        <f t="shared" ref="O2:O8" si="0">SUM(B2:N2)</f>
-        <v>233707.66</v>
+        <f>SUM(B2:N2)</f>
+        <v/>
       </c>
     </row>
-    <row r="3" ht="22.5" customHeight="1" spans="1:15">
-      <c r="A3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="3">
+    <row r="3" ht="22.5" customHeight="1" s="6">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>乌兰察布储能项目</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
         <v>84563.17</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="4" t="n">
         <v>4075</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4">
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n">
         <v>1866</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
       <c r="O3" s="4">
-        <f t="shared" si="0"/>
-        <v>90504.17</v>
+        <f>SUM(B3:N3)</f>
+        <v/>
       </c>
     </row>
-    <row r="4" ht="22.5" customHeight="1" spans="1:15">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="3">
+    <row r="4" ht="22.5" customHeight="1" s="6">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>大唐雷州发电项目</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
         <v>33282.29</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
       <c r="O4" s="4">
-        <f t="shared" si="0"/>
-        <v>33282.29</v>
+        <f>SUM(B4:N4)</f>
+        <v/>
       </c>
     </row>
-    <row r="5" ht="22.5" customHeight="1" spans="1:15">
-      <c r="A5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="3">
+    <row r="5" ht="22.5" customHeight="1" s="6">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>新疆慧能项目</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
         <v>415865.5</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="4" t="n">
         <v>104194.7</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4">
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n">
         <v>7619.48</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4">
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n">
         <v>11808.51</v>
       </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4">
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n">
         <v>23323.49</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="4" t="n">
         <v>20867.74</v>
       </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
       <c r="O5" s="4">
-        <f t="shared" si="0"/>
-        <v>583679.42</v>
+        <f>SUM(B5:N5)</f>
+        <v/>
       </c>
     </row>
-    <row r="6" ht="22.5" customHeight="1" spans="1:15">
-      <c r="A6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
+    <row r="6" ht="22.5" customHeight="1" s="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>龙源纸业项目</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
       <c r="O6" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUM(B6:N6)</f>
+        <v/>
       </c>
     </row>
-    <row r="7" ht="22.5" customHeight="1" spans="1:15">
-      <c r="A7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4">
+    <row r="7" ht="22.5" customHeight="1" s="6">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>内蒙古宜化项目</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n">
         <v>22699.11</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="4" t="n">
         <v>14329.2</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="4" t="n">
         <v>17225.67</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="4" t="n">
         <v>19638</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="4" t="n">
         <v>15168.14</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="4" t="n">
         <v>8008.85</v>
       </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
       <c r="O7" s="4">
-        <f t="shared" si="0"/>
-        <v>97068.97</v>
+        <f>SUM(B7:N7)</f>
+        <v/>
       </c>
     </row>
-    <row r="8" ht="22.5" customHeight="1" spans="1:15">
-      <c r="A8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4">
+    <row r="8" ht="22.5" customHeight="1" s="6">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>福建南平项目</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n">
         <v>2110.22</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="4" t="n">
         <v>15966.48</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="4" t="n">
         <v>19360</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="4" t="n">
         <v>23326.18</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="4" t="n">
         <v>12719.55</v>
       </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
       <c r="O8" s="4">
-        <f t="shared" si="0"/>
-        <v>73482.43</v>
+        <f>SUM(B8:N8)</f>
+        <v/>
       </c>
     </row>
-    <row r="9" spans="1:15">
-      <c r="D9">
-        <f t="shared" ref="D9:J9" si="1">SUM(D2:D8)</f>
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <f t="shared" si="1"/>
-        <v>47328.33</v>
-      </c>
-      <c r="F9">
-        <f t="shared" si="1"/>
-        <v>28955.87</v>
-      </c>
-      <c r="G9">
-        <f t="shared" si="1"/>
-        <v>49769.69</v>
-      </c>
-      <c r="H9">
-        <f t="shared" si="1"/>
-        <v>42677</v>
-      </c>
-      <c r="I9">
-        <f t="shared" si="1"/>
-        <v>65769.14</v>
-      </c>
-      <c r="J9">
-        <f t="shared" si="1"/>
-        <v>45428.89</v>
-      </c>
-      <c r="O9">
+    <row r="9">
+      <c r="D9" s="0">
+        <f>SUM(D2:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="0">
+        <f>SUM(E2:E8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="0">
+        <f>SUM(F2:F8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="0">
+        <f>SUM(G2:G8)</f>
+        <v/>
+      </c>
+      <c r="H9" s="0">
+        <f>SUM(H2:H8)</f>
+        <v/>
+      </c>
+      <c r="I9" s="0">
+        <f>SUM(I2:I8)</f>
+        <v/>
+      </c>
+      <c r="J9" s="0">
+        <f>SUM(J2:J8)</f>
+        <v/>
+      </c>
+      <c r="O9" s="0">
         <f>SUM(O2:O8)</f>
-        <v>1111724.94</v>
+        <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>